--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486981_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486981_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2455</v>
+        <v>1.9704</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4951</v>
+        <v>1.5478</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2496</v>
+        <v>0.4226</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8418</v>
+        <v>1.8418</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9813</v>
+        <v>3.7338</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8606</v>
+        <v>-1.892</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7088</v>
+        <v>3.6084</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9195</v>
+        <v>5.2008</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7893</v>
+        <v>-1.5924</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8669</v>
+        <v>-1.7666</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9382</v>
+        <v>-1.467</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0713</v>
+        <v>-0.2996</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4641</v>
+        <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4715</v>
+        <v>-0.0233</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7823</v>
+        <v>-0.1591</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6891</v>
+        <v>0.1358</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.4518</v>
+        <v>1.1786</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.9159</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.5359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0273</v>
+        <v>0.1072</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2426</v>
+        <v>2.2039</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2153</v>
+        <v>-2.0967</v>
       </c>
       <c r="G3" t="n">
         <v>3.0847</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1108</v>
+        <v>-0.031</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2171</v>
+        <v>-0.2559</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1063</v>
+        <v>0.2249</v>
       </c>
       <c r="V3" t="n">
         <v>-2.9466</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003</v>
+        <v>-0.3052</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0639</v>
+        <v>-1.3245</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0669</v>
+        <v>1.0193</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8418</v>
+        <v>-0.4939</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7338</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.892</v>
+        <v>-0.4843</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6084</v>
+        <v>1.5225</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2008</v>
+        <v>1.7072</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5924</v>
+        <v>-0.1847</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7666</v>
+        <v>-2.0165</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.467</v>
+        <v>-1.7168</v>
       </c>
       <c r="O4" t="n">
         <v>-0.2996</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>-4.1068</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9907</v>
+        <v>0.2073</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7708</v>
+        <v>-0.1591</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2199</v>
+        <v>0.3664</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5724</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.0256</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.598</v>
+        <v>-0.5684</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7975</v>
@@ -844,13 +844,13 @@
         <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3909</v>
+        <v>-0.3613</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9667</v>
+        <v>-0.7881</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.37</v>
+        <v>0.8172</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5967</v>
+        <v>-1.6053</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1759</v>
+        <v>3.8418</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3341</v>
+        <v>2.9813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8418</v>
+        <v>0.8606</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3154</v>
+        <v>4.7088</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2759</v>
+        <v>3.9195</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0395</v>
+        <v>0.7893</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4913</v>
+        <v>-0.8669</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6101</v>
+        <v>-0.9382</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8813</v>
+        <v>0.0713</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2053</v>
+        <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3185</v>
+        <v>0.4378</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6587</v>
+        <v>0.1044</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3403</v>
+        <v>0.3334</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3491</v>
+        <v>-4.4518</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.9159</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3491</v>
+        <v>-3.5359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9762</v>
+        <v>-1.5146</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9363</v>
+        <v>-0.8586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9601</v>
+        <v>-0.656</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4939</v>
+        <v>-1.1759</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.3341</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4843</v>
+        <v>-0.8418</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5225</v>
+        <v>0.3154</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7072</v>
+        <v>0.2759</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1847</v>
+        <v>0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0165</v>
+        <v>-1.4913</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7168</v>
+        <v>-0.6101</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2996</v>
+        <v>-0.8813</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4374</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4637</v>
+        <v>0.1337</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7708</v>
+        <v>-0.1473</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3071</v>
+        <v>0.281</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4189</v>
+        <v>0.3491</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4516</v>
+        <v>-2.5709</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0515</v>
+        <v>-2.5436</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5999</v>
+        <v>-0.0273</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.3174</v>
+        <v>-2.7171</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4306</v>
+        <v>-0.3281</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8868</v>
+        <v>-2.389</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.1946</v>
+        <v>-1.1137</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.655</v>
+        <v>0.8599</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.5396</v>
+        <v>-1.9737</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1228</v>
+        <v>-1.6034</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7756</v>
+        <v>-1.188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3472</v>
+        <v>-0.4154</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8658</v>
+        <v>-0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1698</v>
+        <v>-0.6434</v>
       </c>
       <c r="U8" t="n">
-        <v>0.696</v>
+        <v>0.2434</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.506</v>
+        <v>-4.221</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.384</v>
+        <v>-4.7023</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.122</v>
+        <v>0.4813</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.8185</v>
+        <v>-5.3174</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1872</v>
+        <v>-1.4306</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.6313</v>
+        <v>-3.8868</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.2512</v>
+        <v>-4.1946</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1065</v>
+        <v>-0.655</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.1446</v>
+        <v>-3.5396</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5673</v>
+        <v>-1.1228</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0807</v>
+        <v>-0.7756</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4866</v>
+        <v>-0.3472</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1502</v>
+        <v>1.0964</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8672</v>
+        <v>0.5191</v>
       </c>
       <c r="U9" t="n">
-        <v>0.283</v>
+        <v>0.5774</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9651</v>
+        <v>-4.9918</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.671</v>
+        <v>-3.5733</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2941</v>
+        <v>-1.4184</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7171</v>
+        <v>-5.8185</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3281</v>
+        <v>-1.1872</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.389</v>
+        <v>-4.6313</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1137</v>
+        <v>-4.2512</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8599</v>
+        <v>-0.1065</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9737</v>
+        <v>-4.1446</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6034</v>
+        <v>-1.5673</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.188</v>
+        <v>-1.0807</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4154</v>
+        <v>-0.4866</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7942</v>
+        <v>0.6644</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7708</v>
+        <v>0.6778</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0234</v>
+        <v>-0.0134</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4805</v>
+        <v>-1.0698</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7207</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="11">
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.1622</v>
+        <v>-12.8568</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.7134</v>
+        <v>-8.407800000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4488</v>
+        <v>-4.4489</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.552</v>
+        <v>-7.551999999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1843</v>
+        <v>4.184300000000001</v>
       </c>
       <c r="I11" t="n">
         <v>-11.7361</v>
       </c>
       <c r="J11" t="n">
-        <v>4.239299999999998</v>
+        <v>4.239300000000001</v>
       </c>
       <c r="K11" t="n">
         <v>11.9254</v>
@@ -1297,7 +1297,7 @@
         <v>-11.7914</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.7413</v>
+        <v>-7.741300000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-4.05</v>
@@ -1312,13 +1312,13 @@
         <v>13.3471</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5812999999999997</v>
+        <v>1.724</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.5006</v>
+        <v>-0.1952</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9193</v>
+        <v>1.9194</v>
       </c>
       <c r="V11" t="n">
         <v>-6.0021</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.749</v>
+        <v>6.6933</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8905</v>
+        <v>2.5767</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8586</v>
+        <v>4.1166</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1599</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0054</v>
+        <v>-0.0503</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1785</v>
+        <v>-0.4923</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1839</v>
+        <v>0.442</v>
       </c>
       <c r="V12" t="n">
         <v>4.2341</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.085</v>
+        <v>4.6562</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5298</v>
+        <v>2.9021</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5553</v>
+        <v>1.754</v>
       </c>
       <c r="G13" t="n">
         <v>1.7092</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8686</v>
+        <v>0.4398</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8096</v>
+        <v>0.182</v>
       </c>
       <c r="U13" t="n">
-        <v>0.059</v>
+        <v>0.2578</v>
       </c>
       <c r="V13" t="n">
         <v>1.0698</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7458</v>
+        <v>3.6291</v>
       </c>
       <c r="E14" t="n">
-        <v>2.997</v>
+        <v>2.474</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7488</v>
+        <v>1.1551</v>
       </c>
       <c r="G14" t="n">
         <v>2.7234</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4064</v>
+        <v>0.2896</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4725</v>
+        <v>-0.0505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.3401</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5011</v>
+        <v>3.6126</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7306</v>
+        <v>1.9398</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7705</v>
+        <v>1.6728</v>
       </c>
       <c r="G15" t="n">
         <v>5.236</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2626</v>
+        <v>-0.1511</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6201</v>
+        <v>-0.4109</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3575</v>
+        <v>0.2598</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7186</v>
+        <v>2.9575</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0358</v>
+        <v>2.245</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6828</v>
+        <v>0.7125</v>
       </c>
       <c r="G16" t="n">
         <v>2.6299</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1352</v>
+        <v>0.1037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8563</v>
+        <v>-0.6471</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7212</v>
+        <v>0.7508</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4189</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9453</v>
+        <v>2.0987</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0586</v>
+        <v>0.6862</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8868</v>
+        <v>1.4125</v>
       </c>
       <c r="G17" t="n">
         <v>2.5085</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>0.517</v>
+        <v>0.6703</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.178</v>
+        <v>-0.5504</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6949</v>
+        <v>1.2207</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0229</v>
+        <v>-0.7544</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0731</v>
+        <v>-0.8639</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0502</v>
+        <v>0.1095</v>
       </c>
       <c r="G18" t="n">
         <v>0.1037</v>
@@ -1858,13 +1858,13 @@
         <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3053</v>
+        <v>-0.0368</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0659</v>
+        <v>0.1433</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2394</v>
+        <v>-0.1801</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1191</v>
+        <v>-0.821</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1737</v>
+        <v>0.0355</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9454</v>
+        <v>-0.8565</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1861</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1383</v>
+        <v>0.1598</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1976</v>
+        <v>0.0116</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7893</v>
+        <v>-2.729</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1389</v>
+        <v>-2.8711</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3496</v>
+        <v>0.1421</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4336</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2255</v>
+        <v>0.2858</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0731</v>
+        <v>0.3409</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1524</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9384</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6514</v>
+        <v>-3.4833</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4077</v>
+        <v>-4.6755</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7563</v>
+        <v>1.1922</v>
       </c>
       <c r="G21" t="n">
         <v>-5.5791</v>
@@ -2092,13 +2092,13 @@
         <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6</v>
+        <v>-0.4319</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.178</v>
+        <v>-0.4457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4221</v>
+        <v>0.0138</v>
       </c>
       <c r="V21" t="n">
         <v>2.117</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.1621</v>
+        <v>15.8597</v>
       </c>
       <c r="E22" t="n">
-        <v>4.4489</v>
+        <v>4.448799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7135</v>
+        <v>11.4108</v>
       </c>
       <c r="G22" t="n">
         <v>7.552</v>
@@ -2170,13 +2170,13 @@
         <v>14.3738</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5815000000000001</v>
+        <v>1.2789</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9192</v>
+        <v>-1.9191</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5006</v>
+        <v>3.198</v>
       </c>
       <c r="V22" t="n">
         <v>6.001999999999999</v>
